--- a/AAII_Financials/Quarterly/BCE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BCE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
   <si>
     <t>BCE</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4349000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4418800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4670600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4342800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4461600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4125600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4463300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4419900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4387500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4439000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4901400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4494500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4580900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4474500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4739800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4390100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4331200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4253000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4596900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4323000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4120900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4284400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4721400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4436500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4201500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4427700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4892400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4924600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4670100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4379500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4730200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4270800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>8563700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>4208100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>4492100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>4239800</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>4233100</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>4099300</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>4380400</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>4153800</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2421000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2507400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2505300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2354100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2481900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2328600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2445000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2398300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2404600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2533000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2704000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2503000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2563100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2578700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1735000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1357000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1251800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1256300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1600700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1275600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1203400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1308000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1590100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1370000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1154400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1298500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1664600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1473200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1352900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1337900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1632500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1297100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2582100</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1287300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1511500</v>
-      </c>
-      <c r="AL9" s="3">
-        <v>1248800</v>
       </c>
       <c r="AM9" s="3">
         <v>1248800</v>
       </c>
       <c r="AN9" s="3">
+        <v>1248800</v>
+      </c>
+      <c r="AO9" s="3">
         <v>1249900</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1514900</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1236900</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1928000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1911400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2165400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1988700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1979700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1797100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2018300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2021500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1983000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1906000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2197400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1991500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2017800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1895800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3004800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3033100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3079400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2996700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2996200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3047400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2917500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2976400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3131400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3066600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3047100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3129200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3227800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3451300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3317200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3041600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3097600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2973600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>5981700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2920800</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>2980600</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>2991000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>2984300</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>2849400</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>2865500</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>2917000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,19 +1248,20 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>43800</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1255,11 +1269,11 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>45900</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1267,11 +1281,11 @@
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="3">
         <v>68100</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>8</v>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,252 +1496,261 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-21100</v>
+      </c>
+      <c r="E14" s="3">
         <v>7900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>17500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-2854500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-19800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-3500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>105600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1560400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>75300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>188300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>109000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>23700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>31000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>26600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>124400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>31300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>107900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>10900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>68900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>18500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>123700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>108900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>49500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>39100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>369600</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>30600</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>96700</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>19900</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>46000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>21600</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>192600</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>40000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>34600</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>3000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>96000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>29000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>29800</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>64500</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>15400</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>19200</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>968900</v>
+      </c>
+      <c r="E15" s="3">
         <v>971400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>999200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>939800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>943600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>885000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>868800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>931900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>927900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>932000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>948800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>910700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>930400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>887700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>877400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>860700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>886000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>836800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>870700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>849600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>833900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>850700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>855000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>849400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>865600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>854100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>840500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>892900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>871500</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>839100</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>772500</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>726000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>1505600</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>746800</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>737500</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>719700</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>727100</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>698300</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>679100</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>666100</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3389900</v>
+      </c>
+      <c r="E17" s="3">
         <v>3478900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3759700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3293900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3425600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3213600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3509800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3330200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3332500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3465000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3886000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3413800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3493400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3466300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3947800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3396000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3411200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3235200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3737300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3314800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3287800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3420200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3775100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3443700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3607400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3415000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3892900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3708300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3548000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3406500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3873200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3252700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>6577900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3261100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3592300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3198600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>3217200</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>3198100</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>3445500</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>3121300</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>959100</v>
+      </c>
+      <c r="E18" s="3">
         <v>939900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>910900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1048900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1036000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>912100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>953500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1089600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1055100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>974100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1015400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1080800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1087400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1008100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>792100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>994000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>920000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1017800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>859600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1008100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>833100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>864200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>946300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>992800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>594000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1012700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>999500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1216200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1122100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>973100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>857000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1018100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1985900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>947000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>899700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1041100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>1015800</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>901100</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>934900</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>1032500</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,618 +2085,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>31700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-25100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-31400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-35900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>94600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-14600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>97300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>107300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>76700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>42100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>134800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>90200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>289200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-44300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>23600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-85300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-66500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>93800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>15500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>22200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>62200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>42000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-28600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-15300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-71400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-33000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-26500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>38100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-40400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>68500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>14500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-40000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-121200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-55700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>1500</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-43200</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-11200</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-800</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-31500</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-25400</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1896300</v>
+      </c>
+      <c r="E21" s="3">
         <v>1936400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1941500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2024600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1885100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1811700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1725000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1914200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1906300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1863900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1829400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1901300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1728600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1940100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1693100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1769400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1739600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1948400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1745800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1880000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1729200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1757000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1772700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1826900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1377200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1844900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1825200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2158800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1962700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1890700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1644000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1704100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>3370200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1638100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1638800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1717600</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1733300</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1597200</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1582600</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>1673200</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>330300</v>
+      </c>
+      <c r="E22" s="3">
         <v>318100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>330400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>328100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>324100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>294300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>299500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>325700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>311300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>307200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>302100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>275700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>271100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>254200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>234800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>217200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>198800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>189000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>203600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>201500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>193800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>200500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>212000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>213900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>219700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>217500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>222200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>232100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>221300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>216300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>197100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>185300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>365900</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>180700</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>179400</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>180100</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>177100</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>179800</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>172900</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>174400</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>628800</v>
+      </c>
+      <c r="E23" s="3">
         <v>649100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>607500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3625600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>648200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>654000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>472600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-877900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>610100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>460100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>488400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>702300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>506000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>782000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>580800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>691600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>654700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>922600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>671500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>828900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>701500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>705800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>705700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>763600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>302900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>762300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>750800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1022200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>860400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>825200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>674300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>792800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1498800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>710600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>721900</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>817900</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>827600</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>720600</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>730600</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>832800</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>185900</v>
+      </c>
+      <c r="E24" s="3">
         <v>171200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>146600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>355400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>176000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>178800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>121600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>168800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>122600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>159000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>179600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>206200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>199600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>163400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>129700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>171400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>243500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>184300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>226700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>170700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>190000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>147800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>200900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>75300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>190800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>191000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>264500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>218100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>223200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>185700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>162800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>396700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>176900</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>202400</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>185300</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>221800</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>192100</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>193600</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>218200</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>442900</v>
+      </c>
+      <c r="E26" s="3">
         <v>477800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>460900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3270200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>472200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>475200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>351000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-881600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>441300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>337500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>329400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>522600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>299800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>582400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>417400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>561900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>483300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>679000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>487200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>602200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>530800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>515800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>557900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>562700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>227600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>571500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>559800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>757800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>642300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>602000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>488600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>630000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1102100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>533700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>519500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>632600</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>605800</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>528500</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>537000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>614600</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>392900</v>
+      </c>
+      <c r="E27" s="3">
         <v>441300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>433200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3232100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>424500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>438300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>320400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-915700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>392400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>296900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>289300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>473100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>248500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>535800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>388700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>521100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>440400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>637600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>462700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>560700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>495400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>482100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>524600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>525900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>182800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>529900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>520000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>712200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>597900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>562700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>461200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>591500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1027600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>497600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>488200</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>597600</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>569300</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>493200</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>504700</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>577700</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3200,14 +3261,14 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
@@ -3219,35 +3280,35 @@
         <v>0</v>
       </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>163300</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>4600</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>3100</v>
-      </c>
-      <c r="AB29" s="3">
-        <v>3900</v>
       </c>
       <c r="AC29" s="3">
         <v>3900</v>
       </c>
       <c r="AD29" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AE29" s="3">
         <v>6600</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>5600</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>6900</v>
       </c>
-      <c r="AG29" s="3" t="s">
+      <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
-      </c>
       <c r="AI29" s="3">
         <v>0</v>
       </c>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-31700</v>
+      </c>
+      <c r="E32" s="3">
         <v>25100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>31400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>35900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-94600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>14600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-97300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-107300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-76700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-42100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-134800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-90200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-289200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>44300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-23600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>85300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>66500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-93800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-15500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-22200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-62200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-42000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>28600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>15300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>71400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>33000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>26500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-38100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>40400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-68500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-14500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>40000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>121200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>55700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>43200</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>11200</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>800</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>31500</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>25400</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>420400</v>
+      </c>
+      <c r="E33" s="3">
         <v>467800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>459500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3259400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>453900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>466800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>350300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-882300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>426000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>331600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>325600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>507900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>283200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>569800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>388700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>521100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>440400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>637600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>462700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>560700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>495400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>482100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>687900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>530500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>186000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>533800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>523900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>718800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>603500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>569700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>461200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>591500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1027600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>497600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>488200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>597600</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>569300</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>493200</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>504700</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>577700</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>420400</v>
+      </c>
+      <c r="E35" s="3">
         <v>467800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>459500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3259400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>453900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>466800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>350300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-882300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>426000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>331600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>325600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>507900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>283200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>569800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>388700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>521100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>440400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>637600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>462700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>560700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>495400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>482100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>687900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>530500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>186000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>533800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>523900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>718800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>603500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>569700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>461200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>591500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1027600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>497600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>488200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>597600</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>569300</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>493200</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>504700</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>577700</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>337300</v>
+      </c>
+      <c r="E41" s="3">
         <v>985800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>233400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>333800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>373900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>731900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1092500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1376800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1204100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>708900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>584600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>457600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>679700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>547700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>109700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>534200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>440400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>75600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>153300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1605200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1267100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1957500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>173300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1287200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1214000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2103100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>113100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>800900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>867600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>514200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>323500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>600200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>293600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>902600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>465100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1472800</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>414500</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>391800</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>655300</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>1070100</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4356,37 +4446,37 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>9500</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>278000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>555200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>548000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>516900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>757200</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>8</v>
+      <c r="Q42" s="3">
+        <v>0</v>
       </c>
       <c r="R42" s="3" t="s">
         <v>8</v>
@@ -4394,8 +4484,8 @@
       <c r="S42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -4463,862 +4553,886 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3323000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3490300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3682400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3318300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3296500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3156500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3451400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3283600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3161500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3222800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3387800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3135800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3152100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3138900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3367000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3062200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2924200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2860800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3230200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2894800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2683900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2860800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3261400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2870300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2929400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3161400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3234900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3245700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>797000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>752900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>751200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>658400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2851600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2841000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2947800</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>2131400</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>2117300</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>2164900</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>2288600</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>2473700</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>316200</v>
+      </c>
+      <c r="E44" s="3">
         <v>233500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>283700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>271400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>332100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>293600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>291900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>282800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>299600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>338200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>352100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>470200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>495400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>497400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>482900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>456900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>417500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>412200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>356900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>309600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>302300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>344600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>339700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>325800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>349200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>382300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>332900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>400400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>386200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>363400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>328800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>356800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>328200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>333500</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>282800</v>
-      </c>
-      <c r="AL44" s="3">
-        <v>325200</v>
       </c>
       <c r="AM44" s="3">
         <v>325200</v>
       </c>
       <c r="AN44" s="3">
+        <v>325200</v>
+      </c>
+      <c r="AO44" s="3">
         <v>328800</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>309600</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>322700</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>990100</v>
+      </c>
+      <c r="E45" s="3">
         <v>938500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>926300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>878700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>876900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>991400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>907700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>783200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>761300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>762900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>724700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>666800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>635100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>833700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>815600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>929200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>875000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>879700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>848500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>776300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>770200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>760600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>626700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1291800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1363100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>875300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>623000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>738700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>733500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>753700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>717700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>603900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>709900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>639900</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>512800</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>486000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>499400</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>749800</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>476300</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>481700</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5312300</v>
+      </c>
+      <c r="E46" s="3">
         <v>5998500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5402200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5058500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5181600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5412700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6201500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6524300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6270400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5834000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5980500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4980200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5260500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5297100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4775100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4982500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4657100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4228300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4588800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5585900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5023500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5923500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4401100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>5775100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>5855700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6522200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4303800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>5185700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>5145900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4645100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4409000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4361600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>4183300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>4717000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>4208500</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>4415400</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>3356400</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>3635300</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>3729800</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>4348200</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1484400</v>
+      </c>
+      <c r="E47" s="3">
         <v>1414200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1162600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>931900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>921600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>847400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>846500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>698000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>672900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>667600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>689100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>408800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>413100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>653400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1425100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>628200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>642900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>655000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>680400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>690400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>690700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>736600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1417500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1296400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1216300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>927900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>959800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>995700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>964300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>985400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>992500</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>879300</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>916100</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>935700</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>926500</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>616200</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>657100</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>675300</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>654500</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>793600</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>23218800</v>
+      </c>
+      <c r="E48" s="3">
         <v>23732300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>24462500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>23521600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21644500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>20716600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>20850800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>22143700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21963200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>22418200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>22983000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>22293800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>22586500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>21605900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>21535600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>20750000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>20807700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>20434800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>20904100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>20611100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>19927600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>20551000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>21288200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>20743000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>21062400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>21535500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>21547000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>22698600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>21740600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>20997600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>18908500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>17968100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>18362100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>18194200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>17882600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>17678000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>17552900</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>18015000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>17166900</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>16807300</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>21838600</v>
+      </c>
+      <c r="E49" s="3">
         <v>22119700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>22219100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>22016100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>19732200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>18775500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>18797800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>20069600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>21178500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>20505600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>20862000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>20339300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>20704600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>20079700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>19940500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>19576700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>19711800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>19301400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>19354500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>17737000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>17243000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>17895200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>18342500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>18003000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>18400600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>18982500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>18726900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>20006600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>18957900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>18418700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>18161900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>17450700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>18048100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>18031600</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>17627400</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>17799300</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>17711500</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>18239300</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>16099000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>15574300</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4280700</v>
+      </c>
+      <c r="E52" s="3">
         <v>4044800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3901900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3844500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3685100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3519000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3183100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3490900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3296700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3324700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2772200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3188300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3153600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3346600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3357400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4026400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4453900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4333700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3901700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4513300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3496000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3135600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1490200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1424400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1483900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3464400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1356600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1375400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>941300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1019200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>986400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1236800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1067500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>765600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>883400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>843200</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>605800</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>803600</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>844300</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>695200</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>57067800</v>
+      </c>
+      <c r="E54" s="3">
         <v>58298800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>58466800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>56417200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>52156400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>50204900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>51072400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>53825800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>54248300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>53589800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>54474000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>52021400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>52899100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>51718000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>51033800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>49963800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>50273500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>48953200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>49429400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>49137700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>46380800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>48242000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>46939500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>47241900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>48019000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>51432600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>46894000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>50262000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>47750100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>46066000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>43458200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>41896600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>42577000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>42644000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>41528400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>41352000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>39883700</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>41368400</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>38494500</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>38218700</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2934300</v>
+      </c>
+      <c r="E57" s="3">
         <v>2949400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2054500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2999500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3144000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2876100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2057900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3034200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3172500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3208700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2504900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3218600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3282700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3015500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3843200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3353800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3139200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2792400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3298300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3060000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2823500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2795500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3044700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2733800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2621800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2618100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3082800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3026000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2950000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2779100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2999500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2745400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2712300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2660400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>2883800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>3326600</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>3177800</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>3106700</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>3323400</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>3092100</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2995600</v>
+      </c>
+      <c r="E58" s="3">
         <v>3949500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4489000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4178400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3693200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3703300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5330000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5533100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4812800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4716000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3817900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3822600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4560500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4691000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3045300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3415000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2445300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2240600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1943400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1477000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1666300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2842800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1870200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2226300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2027800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3304300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3025900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3919700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>4501200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>4222500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3535300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3544100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>4315000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>4155400</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>3853500</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>4527000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>4420600</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>4844500</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>3754300</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>3834200</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1002700</v>
+      </c>
+      <c r="E59" s="3">
         <v>1042400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1889700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1364100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1342500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1655100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2069700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1647000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1312200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1432700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2005900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1468900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1434800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1495900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1553900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1548600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1619900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1485300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1505200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1391900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1551300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1515200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1484800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1615300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1734300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1468000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1514100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1657300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1543200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1454200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1402700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1301500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1289500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1228600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1249500</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>804500</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>743500</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>672200</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>687600</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>689900</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7250200</v>
+      </c>
+      <c r="E60" s="3">
         <v>8143400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9376300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8743700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8486900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8432200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10318000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10457800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9587500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>9604800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9167600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8700800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>9508400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>9356200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8442400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8317300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7204400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6518400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6746900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5928900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6041100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7153400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>6399700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>6575500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>6383900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>7390500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>7622800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>8603100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8994400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>8455700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>7937400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>7591000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>8316800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>8044300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>7986900</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>8658100</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>8341800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>8623400</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>7765300</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>7616200</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>26422100</v>
+      </c>
+      <c r="E61" s="3">
         <v>26827200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>25456600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>25238900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>23845600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>23563500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>22820500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>24135600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>24051400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>23102100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>23575900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>21831100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>21382000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>20292500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>20451300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>19506700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>19957900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>19539800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>20025300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>20051800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>18385700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>18745200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>18497300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>19100100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>19637300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>20029000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>17476300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>18608000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>17406000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>16948400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>15039100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>14231500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>13826500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>14564200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>13555800</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>13735100</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>12973800</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>13641500</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>12731100</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>12679600</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>816100</v>
+      </c>
+      <c r="E62" s="3">
         <v>846800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1068500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1006500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1184900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1155600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1144000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>863100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1042600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1049400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1300100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>970600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>907000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>762700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5566500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>5392100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>5549100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>5603100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>5672600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>5743000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>5487100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>5549600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>5539300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>5405600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>5410800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>5624100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>5103700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>5422800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>5123700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>4851400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>4735500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>4709700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>4832900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>4756900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>4636400</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>4340200</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>4371500</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>4358900</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>4282100</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>5051900</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>40042300</v>
+      </c>
+      <c r="E66" s="3">
         <v>41353700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>41466100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>40078500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>38682100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>37946900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>39007100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>40515900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>39628100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>38545300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>38907900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>36270600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>36701400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>35260600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>34708300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>33463900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>32953800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>31892500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>32671300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>31983700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>30159700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>31702800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>30699300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>31350200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>31705100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>33310500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>30463300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>32912500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>31785000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>30493300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>27960200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>26767600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>27216400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>27597300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>26419500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>26975400</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>25928300</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>26866500</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>25019700</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>25588200</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,112 +7688,115 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>2264600</v>
+      </c>
+      <c r="E70" s="3">
         <v>2328300</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>2398000</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>2396500</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>2510500</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>2421800</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>2455500</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>2634400</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>2600400</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>2668900</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>2776700</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>2766200</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>2855300</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>2828500</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>2848700</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>2831200</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>2871000</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>2824400</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>2963700</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>2965200</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>2895000</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>3005700</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>3097300</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>3069600</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>3142100</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>3143300</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>3121800</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>3319500</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>3175300</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>3082400</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AH70" s="3">
         <v>3047400</v>
       </c>
-      <c r="AH70" s="3">
+      <c r="AI70" s="3">
         <v>2909700</v>
-      </c>
-      <c r="AI70" s="3">
-        <v>3014200</v>
       </c>
       <c r="AJ70" s="3">
         <v>3014200</v>
       </c>
       <c r="AK70" s="3">
-        <v>2979800</v>
+        <v>3014200</v>
       </c>
       <c r="AL70" s="3">
         <v>2979800</v>
@@ -7637,7 +7805,7 @@
         <v>2979800</v>
       </c>
       <c r="AN70" s="3">
-        <v>3076000</v>
+        <v>2979800</v>
       </c>
       <c r="AO70" s="3">
         <v>3076000</v>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>3076000</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>3076000</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1477400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1844000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2656200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2917700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-6148000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-6009700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-5866500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-5943200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-4364900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-4217500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-4174500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-3486200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-3487400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-2901700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-2686100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-2371400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-2001900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1992000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-2517200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-2194100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-2459700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-2772900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-3621900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-3899900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-4035100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-2347300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-3611400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-3925600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-4119700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-3860600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-3757500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-3181400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-3621700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-3908500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-3674900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-4370700</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-4812100</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-4858300</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>-4640100</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>-5443700</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>14539800</v>
+      </c>
+      <c r="E76" s="3">
         <v>14406900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>14391200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>13726900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10736400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9637200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9409000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>10451200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11788300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>12137000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>12541000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>12735500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13094700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13382800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13476700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13668600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>14448700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>14236300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13794400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>14188900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13326100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13533500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>13142900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>12822100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>13171900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>14978800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>13309000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>14030000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>12789800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>12490300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>12450700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>12219300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>12346500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>12032600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>12129100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>11396800</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>10975600</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>11425900</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>10398800</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>9554500</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>420400</v>
+      </c>
+      <c r="E81" s="3">
         <v>467800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>459500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3259400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>453900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>466800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>350300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-882300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>426000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>331600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>325600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>507900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>283200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>569800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>388700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>521100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>440400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>637600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>462700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>560700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>495400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>482100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>687900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>530500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>186000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>533800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>523900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>718800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>603500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>569700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>461200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>591500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1027600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>497600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>488200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>597600</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>569300</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>493200</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>504700</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>577700</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>695800</v>
+      </c>
+      <c r="E83" s="3">
         <v>654700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>75100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>691400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>690500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>698600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>166600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>692700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>706800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>678500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>196500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>665700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>724400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>713700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>877400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>860700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>886000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>836800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>870700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>849600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>833900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>850700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>855000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>849400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>854600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>865100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>852200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>904500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>881000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>849100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>772500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>726000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>1505600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>746800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>736800</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>724100</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>729300</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>696800</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>679100</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>666100</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1522400</v>
+      </c>
+      <c r="E89" s="3">
         <v>823100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1138500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1374100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1427600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1093000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1304500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1363500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1561400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>836000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1796900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1449600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1786000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>921600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1476600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1454600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1919200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1247500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1290400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1314100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1807300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1495700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1265100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1617600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2010500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1139100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1630300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1872000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1659800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1167000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1360800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1484600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2674700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1126200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1233900</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1661800</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1603000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1008700</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1167700</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>1492700</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-760500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-602500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-960500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-639700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-559400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-507200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-669300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-706200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-714600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-740000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-779200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-856800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-987000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-802700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1635000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1320000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1219000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-959000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1033000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1582000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-872900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-759900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1156000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-790400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-701600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-614700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-899000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-839800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-770800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-654300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-741300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-734000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-1495800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-700800</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-818600</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-774000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-775500</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-654500</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-762900</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-749800</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-793600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-647600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-948900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-868700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-549900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-235900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-419800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-775800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1379500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-663200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1558300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-869300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1099500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-806400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1427300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-970700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-885300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-761900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2329200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1177000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-893200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-775600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-491300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-897700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-740800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-620200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-906000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-837300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-785100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-672800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-717700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-864000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1696800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-871000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-848400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-801500</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-538800</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-1917500</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-838100</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-1139300</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,130 +10455,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>287300</v>
+      </c>
+      <c r="E96" s="3">
         <v>292300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>297600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>292900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>445800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>418800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>632500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>673600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>664900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>652100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>667900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>652700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>666100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>620100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-617600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-611400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-620000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-578000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-588600</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-587400</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-572100</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-565400</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-582600</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-577300</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-590900</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-562100</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-558200</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-591100</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-564600</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-521900</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-515300</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-492700</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-996700</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-486300</v>
-      </c>
-      <c r="AK96" s="3">
-        <v>-480800</v>
       </c>
       <c r="AL96" s="3">
         <v>-480800</v>
       </c>
       <c r="AM96" s="3">
+        <v>-480800</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-465900</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-456300</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-455600</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-456300</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,130 +10953,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1361900</v>
+      </c>
+      <c r="E100" s="3">
         <v>504300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-294600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-539200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1275100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1218900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1084900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-430800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>320800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-34000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-122700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-788000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-566400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>322200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-516000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-384100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-730900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-560500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-484200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>170400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1462400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1069200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1896500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-618700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2158000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1470400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1364400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1140800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-536900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-307200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-948300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-303800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1154800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>176900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1393200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>198000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-1029200</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>645300</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-744400</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>244300</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10876,8 +11125,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10954,126 +11203,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-631600</v>
+      </c>
+      <c r="E102" s="3">
         <v>679900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-105800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-32300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-397400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-361800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-200200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>156900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>502700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>138800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>115900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-207700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>120100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>437500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-466700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>99800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>303000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-74900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1517000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>303700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-550400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1789300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1122700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>101200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-888300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1989300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-640100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-106100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>337800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>187100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-305200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>316800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-176900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>432100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-1007700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>1058300</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>35000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-263500</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-414800</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>597700</v>
       </c>
     </row>
